--- a/Gerbers/FreeRunner Position File.xlsx
+++ b/Gerbers/FreeRunner Position File.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Armin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Austin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E9F7D4-D4D1-4240-8A39-B592E89EE1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A70499-BE7E-40C8-91EA-3D8066B4CF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E01ADF36-F15D-4E53-8A2C-AD6DB2A84B3E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{E01ADF36-F15D-4E53-8A2C-AD6DB2A84B3E}"/>
   </bookViews>
   <sheets>
     <sheet name="FreeRunner Final Revision-top-p" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,8 +272,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -453,8 +461,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -569,6 +583,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -614,9 +643,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -977,551 +1012,554 @@
   <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" style="1" customWidth="1"/>
-    <col min="2" max="5" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="21.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="1"/>
+    <col min="5" max="5" width="16.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="3">
         <v>94.869</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="3">
         <v>-60.8065</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="3">
         <v>92.55</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="3">
         <v>-55.97</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="3">
         <v>105.791</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="3">
         <v>-60.858400000000003</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="3">
         <v>103.575</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="3">
         <v>-56.024999999999999</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="3">
         <v>113.23</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="3">
         <v>-57.3825</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3">
         <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="3">
         <v>87.147400000000005</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="3">
         <v>-55.803800000000003</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="3">
         <v>87.452200000000005</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="3">
         <v>-57.048400000000001</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="3">
         <v>100.38079999999999</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="3">
         <v>-40.3352</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
         <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="3">
         <v>99.136200000000002</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="3">
         <v>-40.1828</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
         <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="3">
         <v>88.341200000000001</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="3">
         <v>-50.876199999999997</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="D11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="3">
         <v>88.646000000000001</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="3">
         <v>-52.095399999999998</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="D12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="3">
         <v>104.8004</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="3">
         <v>-46.913800000000002</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="D13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="3">
         <v>104.4194</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="3">
         <v>-45.669199999999996</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="3">
         <v>96.38</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="3">
         <v>-37.854999999999997</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3">
         <v>-90</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="3">
         <v>90.81</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="3">
         <v>-37.921599999999998</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="D16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="3">
         <v>-90</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="3">
         <v>93.584800000000001</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="3">
         <v>-37.884300000000003</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3">
         <v>-90</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="1">
-        <v>79.25</v>
-      </c>
-      <c r="C18" s="1">
+      <c r="B18" s="3">
+        <v>84.75</v>
+      </c>
+      <c r="C18" s="3">
         <v>-45.95</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="3">
+        <v>87.802499999999995</v>
+      </c>
+      <c r="C19" s="3">
+        <v>-47.22</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="3">
+        <v>87.67</v>
+      </c>
+      <c r="C20" s="3">
+        <v>-39.6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="3">
+        <v>87.71</v>
+      </c>
+      <c r="C21" s="3">
+        <v>-42.14</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="3">
+        <v>96.38</v>
+      </c>
+      <c r="C22" s="3">
+        <v>-40.619999999999997</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="3">
+        <v>90.81</v>
+      </c>
+      <c r="C23" s="3">
+        <v>-40.68</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="3">
+        <v>93.58</v>
+      </c>
+      <c r="C24" s="3">
+        <v>-40.732500000000002</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="3">
+        <v>107.04</v>
+      </c>
+      <c r="C25" s="3">
+        <v>-54.5</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="3">
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="1">
-        <v>87.802499999999995</v>
-      </c>
-      <c r="C19" s="1">
-        <v>-47.22</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" s="1">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="3">
+        <v>99.7</v>
+      </c>
+      <c r="C26" s="3">
+        <v>-57.137900000000002</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="3">
+        <v>97.46</v>
+      </c>
+      <c r="C27" s="3">
+        <v>-57.13</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="3">
+        <v>102.88524</v>
+      </c>
+      <c r="C28" s="3">
+        <v>-36.35</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="3">
+        <v>97.523300000000006</v>
+      </c>
+      <c r="C29" s="3">
+        <v>-48.835000000000001</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
+        <v>91.694000000000003</v>
+      </c>
+      <c r="C30" s="3">
+        <v>-59.69</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="3">
+        <v>102.478799</v>
+      </c>
+      <c r="C31" s="3">
+        <v>-59.709049999999998</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="1">
-        <v>87.67</v>
-      </c>
-      <c r="C20" s="1">
-        <v>-39.6</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="1">
-        <v>87.71</v>
-      </c>
-      <c r="C21" s="1">
-        <v>-42.14</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="1">
-        <v>96.38</v>
-      </c>
-      <c r="C22" s="1">
-        <v>-40.619999999999997</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="1">
-        <v>90.81</v>
-      </c>
-      <c r="C23" s="1">
-        <v>-40.68</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="1">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="1">
-        <v>93.58</v>
-      </c>
-      <c r="C24" s="1">
-        <v>-40.732500000000002</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="1">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="1">
-        <v>107.04</v>
-      </c>
-      <c r="C25" s="1">
-        <v>-54.5</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" s="1">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="1">
-        <v>99.7</v>
-      </c>
-      <c r="C26" s="1">
-        <v>-57.137900000000002</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="1">
-        <v>97.46</v>
-      </c>
-      <c r="C27" s="1">
-        <v>-57.13</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="1">
-        <v>102.88524</v>
-      </c>
-      <c r="C28" s="1">
-        <v>-35.953699999999998</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E28" s="1">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="1">
-        <v>97.523300000000006</v>
-      </c>
-      <c r="C29" s="1">
-        <v>-48.835000000000001</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="1">
-        <v>91.694000000000003</v>
-      </c>
-      <c r="C30" s="1">
-        <v>-59.69</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="1">
-        <v>102.478799</v>
-      </c>
-      <c r="C31" s="1">
-        <v>-59.709049999999998</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E31" s="1">
-        <v>90</v>
-      </c>
-    </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="3">
         <v>98.19</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="3">
         <v>-60.75</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
         <v>90</v>
       </c>
     </row>
